--- a/artfynd/A 31414-2025 artfynd.xlsx
+++ b/artfynd/A 31414-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>89595777</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441460.0471339008</v>
+        <v>441460</v>
       </c>
       <c r="R2" t="n">
-        <v>6841137.23363703</v>
+        <v>6841137</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,122 +774,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>89595778</v>
-      </c>
-      <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Svartåsen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>441474.8110623838</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6841250.865365392</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Lillhärdal</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 31414-2025 artfynd.xlsx
+++ b/artfynd/A 31414-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,8 +783,16 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>